--- a/docs/students/11a.xlsx
+++ b/docs/students/11a.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAB73E1-0199-48AF-AF6A-A0B6F580B81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A9E651-3792-488F-A96A-DC7E4D778E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,26 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t xml:space="preserve">CORREO MAMÁ </t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Correo institucional</t>
-  </si>
-  <si>
-    <t>Nombre mamá</t>
-  </si>
-  <si>
-    <t>Nombre papá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREO PAPÁ </t>
-  </si>
-  <si>
     <t xml:space="preserve">Liliana Marcela Angulo Rueda </t>
   </si>
   <si>
@@ -259,6 +244,27 @@
   </si>
   <si>
     <t>23AC0352@cac.edu.co</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CORREO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>NOMBRE MAMÁ</t>
+  </si>
+  <si>
+    <t>NOMBRE  PAPÁ</t>
+  </si>
+  <si>
+    <t>CORREO PAPÁ</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -333,7 +339,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -345,9 +351,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -689,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -698,57 +701,78 @@
     <col min="4" max="4" width="30.25" customWidth="1"/>
     <col min="5" max="5" width="28.25" customWidth="1"/>
     <col min="6" max="6" width="30.375" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="78.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="74.099999999999994" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+    <row r="1" spans="1:7" ht="15">
+      <c r="A1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="4"/>
+      <c r="G3" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>63</v>
+      <c r="B4" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
@@ -761,26 +785,32 @@
       </c>
       <c r="F4" s="4" t="s">
         <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>64</v>
+      <c r="B5" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -788,80 +818,89 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
+      <c r="G7" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>32</v>
+      <c r="G8" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" t="s">
-        <v>36</v>
+      <c r="G9" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -869,7 +908,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>38</v>
@@ -882,6 +921,9 @@
       </c>
       <c r="F10" s="3" t="s">
         <v>41</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -889,7 +931,7 @@
         <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>43</v>
@@ -902,6 +944,9 @@
       </c>
       <c r="F11" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -909,7 +954,7 @@
         <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>48</v>
@@ -922,14 +967,17 @@
       </c>
       <c r="F12" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>72</v>
+      <c r="B13" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>53</v>
@@ -940,61 +988,44 @@
       <c r="E13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>61</v>
+      <c r="G13" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
-    <hyperlink ref="D10" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="D11" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
-    <hyperlink ref="D12" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
-    <hyperlink ref="F4" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
-    <hyperlink ref="F5" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
-    <hyperlink ref="F6" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
-    <hyperlink ref="F7" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
-    <hyperlink ref="F9" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
-    <hyperlink ref="F10" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
-    <hyperlink ref="F11" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
-    <hyperlink ref="F12" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
-    <hyperlink ref="F13" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
-    <hyperlink ref="F14" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
-    <hyperlink ref="B6" r:id="rId20" display="24AC0508@Australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
-    <hyperlink ref="B7" r:id="rId21" display="23AC0328@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
-    <hyperlink ref="B14" r:id="rId22" display="23AC0352@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000015000000}"/>
-    <hyperlink ref="B4" r:id="rId23" display="23AC0326@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000016000000}"/>
-    <hyperlink ref="B3" r:id="rId24" display="25AC0586@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000017000000}"/>
-    <hyperlink ref="D8" r:id="rId25" xr:uid="{00000000-0004-0000-0600-000018000000}"/>
-    <hyperlink ref="F8" r:id="rId26" xr:uid="{00000000-0004-0000-0600-000019000000}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="F3" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="F4" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="F5" r:id="rId12" xr:uid="{00000000-0004-0000-0600-00000B000000}"/>
+    <hyperlink ref="F6" r:id="rId13" xr:uid="{00000000-0004-0000-0600-00000C000000}"/>
+    <hyperlink ref="F8" r:id="rId14" xr:uid="{00000000-0004-0000-0600-00000D000000}"/>
+    <hyperlink ref="F9" r:id="rId15" xr:uid="{00000000-0004-0000-0600-00000E000000}"/>
+    <hyperlink ref="F10" r:id="rId16" xr:uid="{00000000-0004-0000-0600-00000F000000}"/>
+    <hyperlink ref="F11" r:id="rId17" xr:uid="{00000000-0004-0000-0600-000010000000}"/>
+    <hyperlink ref="F12" r:id="rId18" xr:uid="{00000000-0004-0000-0600-000011000000}"/>
+    <hyperlink ref="F13" r:id="rId19" xr:uid="{00000000-0004-0000-0600-000012000000}"/>
+    <hyperlink ref="B5" r:id="rId20" display="24AC0508@Australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000013000000}"/>
+    <hyperlink ref="B6" r:id="rId21" display="23AC0328@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000014000000}"/>
+    <hyperlink ref="B13" r:id="rId22" display="23AC0352@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000015000000}"/>
+    <hyperlink ref="B3" r:id="rId23" display="23AC0326@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000016000000}"/>
+    <hyperlink ref="B2" r:id="rId24" display="25AC0586@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0600-000017000000}"/>
+    <hyperlink ref="D7" r:id="rId25" xr:uid="{00000000-0004-0000-0600-000018000000}"/>
+    <hyperlink ref="F7" r:id="rId26" xr:uid="{00000000-0004-0000-0600-000019000000}"/>
+    <hyperlink ref="G2" r:id="rId27" xr:uid="{27416DDE-001B-4E94-91C5-7152059F5D63}"/>
+    <hyperlink ref="G3:G12" r:id="rId28" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{AD6F1810-43B6-4732-A155-C06CC83A6AAF}"/>
+    <hyperlink ref="G13" r:id="rId29" xr:uid="{CEFC6E64-2481-43D9-B703-5F74F26A0BD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
